--- a/testcases/Failed_Test_Cases.xlsx
+++ b/testcases/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,38 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-        <bgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,38 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,228 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Error</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Authentication Spec #40</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Registration</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Registration Spec #10</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Navigation Spec #10</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Dashboard Spec #20</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Forms Spec #40</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>CRUD Operations</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium CRUD Operations Spec #40</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Filters</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Filters Spec #20</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Input Validation</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Input Validation Spec #40</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Session Management</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Session Management Spec #20</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Android Appium Regression Suite Spec #02</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Appium element location timeout on Android viewport</t>
         </is>
       </c>
     </row>
